--- a/data/trans_camb/P36B08_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P36B08_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32,19</t>
+          <t>32,72</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,26</t>
+          <t>25,19</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28,3</t>
+          <t>29,05</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 17,9</t>
+          <t>1,89; 18,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,23; 27,52</t>
+          <t>10,39; 26,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,81; 39,24</t>
+          <t>26,16; 39,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 15,18</t>
+          <t>-0,45; 15,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,88; 21,51</t>
+          <t>7,06; 21,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,15; 30,74</t>
+          <t>19,28; 31,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 14,13</t>
+          <t>2,83; 14,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,4; 21,84</t>
+          <t>11,53; 21,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,39; 33,35</t>
+          <t>24,6; 33,69</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 31,59</t>
+          <t>2,75; 33,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,43; 49,29</t>
+          <t>16,03; 47,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38,14; 71,76</t>
+          <t>38,9; 71,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 22,36</t>
+          <t>-0,57; 24,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,22; 32,03</t>
+          <t>9,38; 32,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,89; 47,5</t>
+          <t>25,29; 47,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 22,42</t>
+          <t>4,06; 22,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,86; 34,79</t>
+          <t>16,69; 34,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33,62; 53,71</t>
+          <t>35,05; 54,19</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47,28</t>
+          <t>47,59</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,57</t>
+          <t>35,91</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>41,36</t>
+          <t>41,69</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 17,91</t>
+          <t>4,22; 17,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,18; 28,75</t>
+          <t>16,58; 28,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41,76; 52,92</t>
+          <t>41,74; 52,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 15,85</t>
+          <t>3,81; 15,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,63; 26,86</t>
+          <t>15,06; 26,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,66; 40,45</t>
+          <t>31,29; 40,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,47; 14,56</t>
+          <t>5,35; 14,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,67; 26,15</t>
+          <t>17,85; 26,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37,72; 44,96</t>
+          <t>38,21; 45,16</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>103,81%</t>
+          <t>104,47%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,7%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,33; 41,97</t>
+          <t>8,29; 40,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,14; 69,95</t>
+          <t>33,42; 68,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83,97; 128,66</t>
+          <t>83,95; 129,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,77; 28,94</t>
+          <t>5,93; 28,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,63; 49,12</t>
+          <t>24,58; 49,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,42; 75,46</t>
+          <t>50,83; 76,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,26; 29,54</t>
+          <t>10,06; 29,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32,52; 53,4</t>
+          <t>32,8; 52,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>69,51; 92,61</t>
+          <t>70,24; 92,57</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18,69</t>
+          <t>19,25</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,37</t>
+          <t>17,59</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18,05</t>
+          <t>18,44</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 14,54</t>
+          <t>0,79; 13,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 7,26</t>
+          <t>-6,49; 7,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,04; 24,05</t>
+          <t>13,38; 24,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 14,92</t>
+          <t>2,86; 14,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 6,98</t>
+          <t>-5,24; 6,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,88; 22,61</t>
+          <t>12,88; 23,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,43; 12,67</t>
+          <t>3,43; 12,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 5,45</t>
+          <t>-4,33; 5,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,22; 21,73</t>
+          <t>14,27; 22,39</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 21,37</t>
+          <t>1,03; 19,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 10,65</t>
+          <t>-8,61; 10,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,73; 35,36</t>
+          <t>17,5; 36,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,95; 20,38</t>
+          <t>3,58; 19,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 9,52</t>
+          <t>-6,57; 9,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,84; 31,23</t>
+          <t>15,89; 31,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,51; 17,57</t>
+          <t>4,46; 17,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 7,44</t>
+          <t>-5,54; 7,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,32; 30,11</t>
+          <t>18,39; 31,41</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29,57</t>
+          <t>29,86</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,74</t>
+          <t>20,31</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>25,1</t>
+          <t>24,99</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,42; 16,74</t>
+          <t>2,12; 16,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,91; 18,64</t>
+          <t>5,09; 17,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24,2; 34,87</t>
+          <t>25,02; 35,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 13,55</t>
+          <t>1,95; 13,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,17; 14,49</t>
+          <t>3,59; 15,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,75; 25,08</t>
+          <t>16,09; 25,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,8; 13,0</t>
+          <t>4,46; 13,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,5; 14,8</t>
+          <t>5,85; 14,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,01; 28,41</t>
+          <t>21,57; 28,45</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,26; 26,09</t>
+          <t>2,97; 25,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,06; 28,9</t>
+          <t>7,14; 28,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33,22; 54,95</t>
+          <t>34,29; 55,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,74; 18,4</t>
+          <t>2,4; 17,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,92; 19,69</t>
+          <t>4,5; 20,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,69; 34,19</t>
+          <t>19,84; 34,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,32; 18,45</t>
+          <t>5,93; 18,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,5; 21,07</t>
+          <t>7,83; 20,31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>28,98; 40,4</t>
+          <t>28,52; 40,62</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48,79</t>
+          <t>48,83</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,65</t>
+          <t>36,68</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>42,64</t>
+          <t>42,68</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,97; 23,44</t>
+          <t>3,49; 22,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>30,35; 46,47</t>
+          <t>29,98; 46,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41,52; 55,19</t>
+          <t>41,74; 55,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,05; 19,72</t>
+          <t>1,09; 18,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,46; 34,74</t>
+          <t>19,21; 35,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,94; 43,19</t>
+          <t>30,01; 43,65</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,1; 18,92</t>
+          <t>5,03; 18,5</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>27,17; 38,58</t>
+          <t>26,57; 38,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38,26; 47,64</t>
+          <t>37,41; 47,27</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,11%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5,19; 51,29</t>
+          <t>6,27; 51,67</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>54,45; 102,49</t>
+          <t>52,96; 107,07</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>71,3; 123,97</t>
+          <t>71,96; 124,71</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2,97; 34,68</t>
+          <t>2,13; 33,19</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>29,26; 62,57</t>
+          <t>27,21; 62,12</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,96; 76,66</t>
+          <t>43,09; 78,25</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,35; 35,75</t>
+          <t>8,22; 34,88</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>43,97; 73,99</t>
+          <t>43,48; 72,99</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>62,3; 91,93</t>
+          <t>60,37; 90,25</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>32,32</t>
+          <t>32,28</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,52</t>
+          <t>21,63</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>26,83</t>
+          <t>26,87</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,41; 15,85</t>
+          <t>-0,47; 15,59</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-18,57; -1,8</t>
+          <t>-18,38; -1,46</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25,99; 38,41</t>
+          <t>26,81; 39,01</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 13,36</t>
+          <t>0,5; 13,68</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-23,88; -7,74</t>
+          <t>-23,98; -8,12</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,28; 27,21</t>
+          <t>16,85; 27,39</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,76; 12,36</t>
+          <t>2,34; 12,91</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-19,29; -7,61</t>
+          <t>-19,16; -7,89</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>22,77; 31,05</t>
+          <t>22,99; 31,07</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,12%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0,67; 26,17</t>
+          <t>-0,82; 25,75</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-27,35; -3,23</t>
+          <t>-27,01; -2,43</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>37,71; 66,12</t>
+          <t>38,52; 66,31</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 18,48</t>
+          <t>0,62; 19,14</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-30,23; -10,83</t>
+          <t>-30,23; -10,92</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19,92; 38,12</t>
+          <t>20,81; 38,53</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,47; 18,52</t>
+          <t>3,31; 19,08</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-26,62; -11,22</t>
+          <t>-26,31; -11,28</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>30,75; 46,51</t>
+          <t>31,01; 46,29</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12,05</t>
+          <t>12,55</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,63</t>
+          <t>16,92</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>15,8</t>
+          <t>14,81</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 3,28</t>
+          <t>-6,42; 3,33</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-17,35; -6,61</t>
+          <t>-17,65; -6,74</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6,86; 16,59</t>
+          <t>8,46; 17,5</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,66; 11,68</t>
+          <t>2,74; 12,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 1,66</t>
+          <t>-8,45; 1,95</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,87; 23,66</t>
+          <t>12,89; 21,02</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 6,66</t>
+          <t>-0,54; 6,47</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-11,31; -3,57</t>
+          <t>-11,04; -3,58</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>12,54; 20,06</t>
+          <t>11,89; 17,83</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 4,47</t>
+          <t>-8,2; 4,63</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-22,43; -9,05</t>
+          <t>-22,46; -8,95</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8,84; 22,86</t>
+          <t>10,93; 24,26</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3,48; 16,14</t>
+          <t>3,52; 16,56</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 2,26</t>
+          <t>-10,93; 2,68</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,37; 33,5</t>
+          <t>16,36; 29,02</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 9,07</t>
+          <t>-0,68; 8,72</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-14,67; -4,89</t>
+          <t>-14,42; -4,8</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>16,22; 27,37</t>
+          <t>15,42; 24,45</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>36,59</t>
+          <t>36,07</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>26,86</t>
+          <t>26,91</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>31,62</t>
+          <t>31,37</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>6,2; 16,05</t>
+          <t>5,98; 15,73</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>9,99; 19,55</t>
+          <t>9,93; 18,93</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>32,74; 40,81</t>
+          <t>32,06; 39,7</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4,56; 13,48</t>
+          <t>4,84; 13,12</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,24; 9,26</t>
+          <t>0,17; 9,15</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>23,36; 30,25</t>
+          <t>23,59; 30,67</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,67; 12,93</t>
+          <t>6,75; 13,1</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>6,89; 12,86</t>
+          <t>6,23; 12,7</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>29,08; 34,15</t>
+          <t>28,73; 33,72</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,16%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>9,69; 27,76</t>
+          <t>9,24; 26,61</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>15,48; 33,69</t>
+          <t>15,27; 32,07</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>50,16; 70,35</t>
+          <t>49,14; 67,93</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6,34; 19,77</t>
+          <t>6,41; 18,85</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,49; 13,62</t>
+          <t>0,26; 13,37</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>31,53; 44,42</t>
+          <t>31,68; 45,36</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,72; 20,03</t>
+          <t>10,02; 20,31</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>10,03; 19,82</t>
+          <t>9,16; 19,66</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>42,19; 53,06</t>
+          <t>41,58; 52,49</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>31,14</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,82</t>
+          <t>24,65</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>27,97</t>
+          <t>27,85</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>5,62; 10,38</t>
+          <t>5,5; 10,13</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>6,87; 11,44</t>
+          <t>6,89; 11,68</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>29,28; 33,31</t>
+          <t>28,99; 33,02</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6,16; 10,49</t>
+          <t>6,31; 10,38</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>4,31; 8,41</t>
+          <t>3,95; 8,23</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>23,11; 26,45</t>
+          <t>22,95; 26,3</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,55; 9,7</t>
+          <t>6,61; 9,82</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>6,07; 9,29</t>
+          <t>6,0; 9,19</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>26,62; 29,41</t>
+          <t>26,63; 29,11</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>8,67; 16,76</t>
+          <t>8,57; 16,44</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>10,68; 18,54</t>
+          <t>10,57; 18,67</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>45,2; 53,98</t>
+          <t>44,77; 53,67</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>8,59; 14,97</t>
+          <t>8,67; 14,8</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>5,96; 12,01</t>
+          <t>5,5; 11,85</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>31,92; 37,86</t>
+          <t>31,67; 37,77</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>9,72; 14,62</t>
+          <t>9,72; 14,82</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>8,92; 14,04</t>
+          <t>8,85; 13,94</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>39,09; 44,47</t>
+          <t>39,03; 44,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P36B08_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P36B08_R-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas</t>
+          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas  [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales]</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
